--- a/artfynd/A 19113-2023 artfynd.xlsx
+++ b/artfynd/A 19113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117863718</v>
+        <v>134765584</v>
       </c>
       <c r="B2" t="n">
-        <v>99156</v>
+        <v>58131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>103023</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ryttartorpskärret, Ög</t>
+          <t>Rodga, Lövdalen, 150 m norr vägskälet., Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563548</v>
+        <v>563709</v>
       </c>
       <c r="R2" t="n">
-        <v>6512543</v>
+        <v>6513038</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120146719</v>
+        <v>117863718</v>
       </c>
       <c r="B3" t="n">
-        <v>97983</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järngölen, Ög</t>
+          <t>Ryttartorpskärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563690</v>
+        <v>563548</v>
       </c>
       <c r="R3" t="n">
-        <v>6513063</v>
+        <v>6512543</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -846,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,33 +859,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6879895</v>
+        <v>120146719</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,30 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>strax SO om Järngölen, Ög</t>
+          <t>Järngölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563650</v>
+        <v>563690</v>
       </c>
       <c r="R4" t="n">
-        <v>6512983</v>
+        <v>6513063</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -944,12 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,26 +959,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6881646</v>
+        <v>6879895</v>
       </c>
       <c r="B5" t="n">
-        <v>97975</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,23 +991,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224361</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6881684</v>
+        <v>6881646</v>
       </c>
       <c r="B6" t="n">
-        <v>97985</v>
+        <v>97975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,19 +1084,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1104,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563670</v>
+        <v>563650</v>
       </c>
       <c r="R6" t="n">
-        <v>6512966</v>
+        <v>6512983</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1163,6 +1167,99 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6881684</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>strax SO om Järngölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563670</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6512966</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-07-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-07-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19113-2023 artfynd.xlsx
+++ b/artfynd/A 19113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134765584</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117863718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146719</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6879895</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6881646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,8 +1290,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6881684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>